--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0025.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0025.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Khi ở trong [Giấc Mơ Tiên Tri], gây Tune Break Hủy - Nhiễu Loạn lên tất cả mục tiêu xung quanh mỗi giây.</t>
+          <t>Khi ở trong [Giấc Mơ Tiên Tri], gây Đoạn Tần Phá Hủy - Nhiễu Loạn lên tất cả mục tiêu xung quanh mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Strain - Shifting mỗi giây. Hiệu ứng này cũng được kích hoạt ngay khi bước vào [Divined Dream].</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Strain - Shifting mỗi giây. Hiệu ứng này cũng được kích hoạt ngay khi bước vào [Giấc Mộng Tiên Tri].</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Strain - Shifting mỗi giây.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Strain - Shifting mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], [Blaze Sigil] gây thêm 1500% Fusion DMG lên mục tiêu, được tính là Sát Thương Đứt Giai Tune.</t>
+          <t>Khi ở trong [Divined Dream], [Blaze Sigil] gây thêm 1500% Sát Thương Fusion lên mục tiêu, được tính là Sát Thương Đứt Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], [Hurricane Sigil] gây thêm 4000% Aero DMG lên mục tiêu, được tính là Sát Thương Đứt Giai Tune.</t>
+          <t>Khi ở trong [Divined Dream], [Hurricane Sigil] gây thêm 4000% Sát Thương Aero lên mục tiêu, được tính là Sát Thương Đứt Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], [Thunder Sigil] gây thêm 4000% Electro DMG lên mục tiêu, được tính là Sát Thương Đứt Giai Tune.</t>
+          <t>Khi ở trong [Divined Dream], [Thunder Sigil] gây thêm 4000% Sát Thương Electro lên mục tiêu, được tính là Sát Thương Đứt Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], [Blizzard Sigil] gây thêm 9000% Glacio DMG lên mục tiêu, được tính là Sát Thương Đứt Giai Tune.</t>
+          <t>Khi ở trong [Divined Dream], [Blizzard Sigil] gây thêm 9000% Sát Thương Glacio lên mục tiêu, được tính là Sát Thương Đứt Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Sát thương Basic Attack tăng thêm {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; DMG Basic Attack tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Sát thương Basic Attack tăng đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; DMG Basic Attack tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sát thương Heavy Attack tăng thêm {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; DMG Đòn Heavy Attack tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sát thương Heavy Attack tăng mạnh.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; DMG Đòn Heavy Attack tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng sát thương Resonance Liberation thêm {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng DMG Resonance Liberation thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng đáng kể sát thương Resonance Liberation.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng đáng kể DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Dùng Intro Skill sẽ nhận được một lượng nhỏ Resonance Energy</t>
+          <t>Dùng Kỹ Năng Khởi Động sẽ nhận được một lượng nhỏ Resonance Energy</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Trong vòng 2 giây sau khi tạo ra viên nguyên tố, Resonator tiếp theo được triệu hồi bằng Thẻ Character sẽ gây sát thương thần thánh (5% HP tối đa của kẻ địch).</t>
+          <t>Trong vòng 2 giây sau khi tạo ra viên nguyên tố, Cộng Hưởng Giả tiếp theo được triệu hồi bằng Thẻ Nhân Vật sẽ gây sát thương thần thánh (5% HP tối đa của kẻ địch).</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu của Resonance Skill giảm 30%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu của Resonance Skill giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu của Resonance Skill giảm.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu của Resonance Skill giảm.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Mỗi kẻ địch thường bị đánh bại, bạn nhận được cộng dồn 2% Tấn Công vĩnh viễn (hiệu lực trong cuộc điều tra này, tối đa 15 lần).</t>
+          <t>Mỗi kẻ địch thường bị đánh bại, bạn nhận được cộng dồn 2% ATK vĩnh viễn (hiệu lực trong cuộc điều tra này, tối đa 15 lần).</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tấn Công tăng vĩnh viễn sau khi đánh bại kẻ địch thông thường.</t>
+          <t>ATK tăng vĩnh viễn sau khi đánh bại kẻ địch thông thường.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Sau mỗi lần Dodge, nhận thêm 18% Phòng Ngự trong 12 giây, tối đa 2 lần cộng dồn.</t>
+          <t>Sau mỗi lần Né Tránh, nhận thêm 18% Phòng Ngự trong 12 giây, tối đa 2 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>DEF tăng sau khi né tránh.</t>
+          <t>Phòng Ngự tăng sau khi Né Tránh.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng 8%.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng 8%.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Tăng Crit. DMG thêm 16%.</t>
+          <t>Crit. DMG tăng thêm 16%.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. DMG tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Sau khi sử dụng Skill Echo, hồi phục 15% HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt; Sau khi sử dụng Kỹ năng Echo, hồi phục 15% HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Phục hồi một lượng nhỏ HP sau khi sử dụng Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Phục hồi một lượng nhỏ HP sau khi sử dụng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sau khi đánh bại mục tiêu, Cooldown chiêu Kỹ Năng Echo giảm 2 giây. Có thể kích hoạt mỗi 4 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Sau khi đánh bại mục tiêu, Thời gian hồi chiêu Kỹ Năng Echo giảm 2 giây. Có thể kích hoạt mỗi 4 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo giảm sau khi đánh bại kẻ địch.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo giảm sau khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 18% trong 10 giây sau khi sử dụng Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 18% trong 10 giây sau khi sử dụng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng nhẹ sau khi sử dụng Kỹ Năng Vọng Âm.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng nhẹ sau khi sử dụng Kỹ Năng Vọng Âm.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo được đặt lại sau khi sử dụng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo được đặt lại sau khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Hiệu ứng Cooldown Kỹ Năng Echo được đặt lại sau khi sử dụng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Hiệu ứng Thời gian hồi Kỹ Năng Echo được đặt lại sau khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi sử dụng Kỹ Năng Echo, sát thương Resonance Skill tăng 40% trong 12 giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi sử dụng Kỹ Năng Echo, DMG Resonance Skill tăng 40% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng sau khi sử dụng Kỹ Năng Vang.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng sau khi sử dụng Kỹ Năng Vang.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sau khi sử dụng Resonance Liberation, Sát Thương Kỹ Năng Echo tăng 60% trong 8 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Sau khi sử dụng Resonance Liberation, Sát Thương Kỹ Năng Echo tăng 60% trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sát thương Kỹ Năng Echo tăng mạnh sau khi sử dụng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; DMG Kỹ Năng Echo tăng mạnh sau khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Khi Kỹ Năng Vang Âm trúng mục tiêu, Cooldown chiêu của Resonance Skill giảm 50%. Hiệu ứng này chỉ kích hoạt mỗi 12 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Khi Kỹ Năng Vang Âm trúng mục tiêu, Thời gian hồi chiêu của Resonance Skill giảm 50%. Hiệu ứng này chỉ kích hoạt mỗi 12 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Hồi chiêu Resonance Skill giảm đáng kể khi Kỹ Năng Vang đánh trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi Resonance Skill giảm đáng kể khi Kỹ Năng Vang đánh trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Phòng Ngự của kẻ địch giảm 60% trong 8 giây sau khi trúng Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Phòng Ngự của kẻ địch giảm 60% trong 8 giây sau khi trúng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Phòng Ngự của kẻ địch giảm mạnh sau khi trúng Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Phòng Ngự của kẻ địch giảm mạnh sau khi trúng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Mỗi 1 Năng lượng Resonance, mỗi đòn tấn công trúng mục tiêu sẽ hồi phục 0.1 Concerto Energy. Có thể kích hoạt mỗi giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Mỗi 1 Năng lượng Cộng Hưởng, mỗi đòn tấn công trúng mục tiêu sẽ hồi phục 0.1 Năng lượng Concerto. Có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Cứ 1 Resonance Energy, Crit. DMG tăng 0.4%.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Cứ 1 Resonance Energy, Crit. DMG tăng 0.4%.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng theo lượng Resonance Energy.</t>
+          <t>Crit. DMG tăng theo lượng Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Tốc độ Basic Attack tăng 8%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tổ Hợp]&lt;/color&gt; Tốc độ Đòn Cơ Bản tăng 8%.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Tốc độ Attack cơ bản tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Tốc độ Tấn Công cơ bản tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Heavy Attack 2</t>
+          <t>Đòn Heavy Attack 2</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Speed Heavy Attack tăng 8%.</t>
+          <t>Tốc Độ Đòn Heavy Attack tăng 8%.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Speed Heavy Attack tăng nhẹ.</t>
+          <t>Tốc Độ Đòn Heavy Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Tăng DMG toàn loại 18%</t>
+          <t>Tăng Sát Thương Chung 18%</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>DMG toàn loại tăng nhẹ.</t>
+          <t>Sát Thương Chung tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Cooldown/Basic Attack 1</t>
+          <t>Hồi Chiêu/Đòn Cơ Bản 1</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tăng 20% Sát thương Basic Attack</t>
+          <t>Tăng 20% DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng nhẹ.</t>
+          <t>DMG Basic Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Đòn Attack 1 Nặng 1</t>
+          <t>Đòn Heavy Attack 1</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Cộng Dồn Sát Thương Heavy Attack 20%</t>
+          <t>Cộng Dồn Sát Thương Đòn Heavy Attack 20%</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng nhẹ.</t>
+          <t>DMG Heavy Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng 36%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng 36%.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Resonance Liberation 9</t>
+          <t>Giải Phống Cộng Hưởng Cấp 9</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Khi HP dưới 50%, Sát Thương Resonance Liberation của cậu tăng 35%.</t>
+          <t>Khi HP dưới 50%, Sát Thương Giải Cứu Cộng Hưởng của cậu tăng 35%.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng mạnh khi HP dưới một nửa.</t>
+          <t>DMG Resonance Liberation tăng mạnh khi HP dưới một nửa.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sát thương Kỹ Năng Echo tăng 50%.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; DMG Kỹ Năng Echo tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sát thương Kỹ Năng Echo tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; DMG Kỹ Năng Echo tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Tốc độ phục hồi STA +50%</t>
+          <t>Tốc độ hồi phục STA +50%</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Sát thương nhận vào giảm 20%.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; DMG nhận vào giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Sát thương nhận vào giảm nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; DMG nhận vào giảm nhẹ.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Sau khi sử dụng Resonance Liberation, tăng Kháng Đứt Tác Động và giảm 20% sát thương nhận vào trong 15 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Sau khi sử dụng Resonance Liberation, tăng Kháng Đứt Tác Động và giảm 20% DMG nhận vào trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Kháng Đứt Tác Động tăng và sát thương nhận vào giảm sau khi sử dụng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Kháng Đứt Tác Động tăng và DMG nhận vào giảm sau khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát thương Đòn Đánh Basic tăng 24% trong 12 giây sau khi kích hoạt Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; DMG Đòn Đánh Cơ Bản tăng 24% trong 12 giây sau khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát Thương Basic Attack tăng vừa phải sau khi kích hoạt Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sát Thương Basic Attack tăng vừa phải sau khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần tấn công trúng mục tiêu, Tấn Công tăng 6% và Phòng Ngự tăng 6% trong 2 giây. Hiệu ứng kích hoạt mỗi 1.5 giây một lần, tối đa 10 lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần tấn công trúng mục tiêu, ATK tăng 6% và Phòng Ngự tăng 6% trong 2 giây. Hiệu ứng kích hoạt mỗi 1.5 giây một lần, tối đa 10 lần.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Tấn Công và Phòng Ngự tăng khi tấn công liên tục, có thể tích lũy.</t>
+          <t>&lt;color=#ffd12f&gt;[Tổ Hợp]&lt;/color&gt; ATK và Phòng Ngự tăng khi tấn công liên tục, có thể tích lũy.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần tấn công trúng mục tiêu, hồi phục HP bằng 10% Tấn Công mỗi 2 giây. Hiệu ứng sẽ mất nếu không tấn công trúng mục tiêu trong 2 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần tấn công trúng mục tiêu, hồi phục HP bằng 10% ATK mỗi 2 giây. Hiệu ứng sẽ mất nếu không tấn công trúng mục tiêu trong 2 giây.</t>
         </is>
       </c>
     </row>
@@ -6621,9 +6621,9 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trúng mục tiêu, triệu hồi quả cầu lửa phát nổ gây 100% Fusion DMG lên mục tiêu, được tính là Sát Thương Basic Attack. Hiệu ứng này có thời gian kích hoạt là 0.8 giây.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trúng mục tiêu, triệu hồi quả cầu lửa phát nổ gây 100% Sát Thương Fusion lên mục tiêu, được tính là Sát Thương Đòn Basic Attack. Hiệu ứng này có thời gian kích hoạt là 0.8 giây.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -6690,9 +6690,9 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trúng mục tiêu, triệu hồi quả cầu lửa phát nổ gây Fusion DMG.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trúng mục tiêu, triệu hồi quả cầu lửa phát nổ gây Sát Thương Fusion.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -6759,9 +6759,9 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; trúng mục tiêu, triệu hồi một cơn lốc tấn công mọi kẻ địch trong phạm vi mỗi 0.1 giây, tối đa 4 lần đánh lên mỗi kẻ địch, mỗi lần gây 100% Aero DMG, được tính là Sát Thương Heavy Attack. Hiệu ứng này có thời gian kích hoạt là 2.4 giây.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; trúng mục tiêu, triệu hồi một cơn lốc tấn công mọi kẻ địch trong phạm vi mỗi 0.1 giây, tối đa 4 lần đánh lên mỗi kẻ địch, mỗi lần gây 100% Sát Thương Aero, được tính là Sát Thương Đòn Heavy Attack. Hiệu ứng này có thời gian kích hoạt là 2.4 giây.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -6828,9 +6828,9 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; trúng mục tiêu, triệu hồi một cơn lốc gây Aero DMG nhiều lần lên mọi kẻ địch trong phạm vi.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; trúng mục tiêu, triệu hồi một cơn lốc gây Sát Thương Aero nhiều lần lên mọi kẻ địch trong phạm vi.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -6896,8 +6896,8 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Khi ở trong [Lucid Dream], nhận hiệu ứng [Carnival]: tăng HP tối đa thêm 2000, và tăng Tấn Công (2.5)/Sát Thương (0.3%)/Crit. DMG (0.4%) &lt;color=Highlight&gt;every 200 HP lost&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Khi ở trong [Giấc Mơ Sáng Suốt], nhận hiệu ứng [Lễ Hội]: tăng HP tối đa thêm 2000, và tăng ATK (2.5)/Sát Thương (0.3%)/Crit. DMG (0.4%) &lt;color=Highlight&gt;cho mỗi 200 HP đã mất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6963,8 +6963,8 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Khi ở trong [Lucid Dream], nhận hiệu ứng [Carnival]: tăng HP tối đa và tăng Tấn Công/Sát Thương/Crit. DMG &lt;color=Highlight&gt;based on HP already lost&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Khi ở trong [Giấc Mơ Sáng Suốt], nhận hiệu ứng [Lễ Hội]: tăng HP tối đa và tăng ATK/Sát Thương/Crit. DMG &lt;color=Highlight&gt;dựa trên lượng HP đã mất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7030,8 +7030,8 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Khi ở trong [Lucid Dream], nhận hiệu ứng [Flow]: Mỗi lần gây sát thương làm tăng &lt;color=Highlight&gt;Crit. Rate&lt;/color&gt; thêm 1.6% và &lt;color=Highlight&gt;DMG dealt&lt;/color&gt; thêm 2.4%, có thể tích lũy tối đa 100 lần. Kết thúc trạng thái Lucid Dream sẽ xóa toàn bộ lượt tích lũy.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Khi ở trong [Giấc Mơ Sáng Suốt], nhận hiệu ứng [Dòng Chảy]: Mỗi lần gây DMG làm tăng &lt;color=Highlight&gt;Crit. Rate&lt;/color&gt; thêm 1.6% và &lt;color=Highlight&gt;Sát Thương Gây Ra&lt;/color&gt; thêm 2.4%, có thể tích lũy tối đa 100 lần. Kết thúc trạng thái Giấc Mơ Sáng Suốt sẽ xóa toàn bộ lượt tích lũy.</t>
         </is>
       </c>
     </row>
@@ -7097,8 +7097,8 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Khi ở trong [Lucid Dream], nhận hiệu ứng [Flow]: gây Sát Thương liên tục sẽ tích lũy &lt;color=Highlight&gt;Crit. Rate and DMG dealt&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Khi ở trong [Giấc Mơ Sáng Suốt], nhận hiệu ứng [Dòng Chảy]: gây Sát Thương liên tục sẽ tích lũy &lt;color=Highlight&gt;Crit. Rate và Sát Thương gây ra&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7165,9 +7165,9 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, triệu hồi sét đánh 5 lần, mỗi lần gây 300% Electro DMG, được tính là Sát Thương Resonance Liberation. Hiệu ứng này có thời gian kích hoạt là 12 giây.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, triệu hồi sét đánh 5 lần, mỗi lần gây 300% Sát Thương Electro, được tính là Sát Thương Resonance Liberation. Hiệu ứng này có thời gian kích hoạt là 12 giây.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -7234,9 +7234,9 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, triệu hồi sét đánh 5 lần gây lượng lớn Electro DMG.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, triệu hồi sét đánh 5 lần gây lượng lớn Sát Thương Electro.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -7303,8 +7303,8 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, kích hoạt Vụ Nổ Băng gây 1000% Glacio DMG, được tính là Sát Thương Resonance Liberation. Điều kiện kích hoạt Vụ Nổ Băng không bị ảnh hưởng bởi các Ẩn Dụ khác.
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;, kích hoạt Vụ Nổ Băng gây 1000% Sát Thương Glacio, được tính là Sát Thương Resonance Liberation. Điều kiện kích hoạt Vụ Nổ Băng không bị ảnh hưởng bởi các Ẩn Dụ khác.
 Hiệu ứng này được tăng cường mạnh mẽ khi ở trạng thái Giấc Mơ Tỉnh.</t>
         </is>
       </c>
@@ -7372,9 +7372,9 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Damage]&lt;/color&gt;
-Khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, kích hoạt Vụ Nổ Băng gây lượng lớn Glacio DMG.
-Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Lucid Dream].</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Sát Thương]&lt;/color&gt;
+Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;, kích hoạt Vụ Nổ Băng gây lượng lớn Sát Thương Glacio.
+Hiệu ứng này được tăng cường mạnh mẽ trong trạng thái [Giấc Mơ Sáng Suốt].</t>
         </is>
       </c>
     </row>
@@ -7440,8 +7440,8 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Status [Lucid Dream] chuyển thành trạng thái [Kỵ Sĩ Thời Gian], mang lại các hiệu ứng sau: làm chậm dòng chảy thời gian xung quanh 90%; mỗi lần gây Sát Thương Basic Attack sẽ sinh ra 1 điểm Năng Lượng Thời Gian; khi &lt;color=Highlight&gt;upon ending the Time Rider status&lt;/color&gt;, tiêu thụ toàn bộ Năng Lượng Thời Gian để tạo vụ nổ, gây 900% Spectro DMG cho mỗi 10 điểm Năng Lượng Thời Gian đã tiêu thụ, với Sát Thương tối thiểu là 125% Spectro. Resonator có thể tích lũy tối đa 100 điểm Năng Lượng Thời Gian.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Trạng thái [Giấc Mơ Sáng Suốt] chuyển thành trạng thái [Kỵ Sĩ Thời Gian], mang lại các hiệu ứng sau: làm chậm dòng chảy thời gian xung quanh 90%; mỗi lần gây Sát Thương Đòn Basic Attack sẽ sinh ra 1 điểm Năng Lượng Thời Gian; khi &lt;color=Highlight&gt;kết thúc trạng thái Kỵ Sĩ Thời Gian&lt;/color&gt;, tiêu thụ toàn bộ Năng Lượng Thời Gian để tạo vụ nổ, gây 900% Sát Thương Spectro cho mỗi 10 điểm Năng Lượng Thời Gian đã tiêu thụ, với Sát Thương tối thiểu là 125% Spectro. Resonator có thể tích lũy tối đa 100 điểm Năng Lượng Thời Gian.</t>
         </is>
       </c>
     </row>
@@ -7507,8 +7507,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power: Status]&lt;/color&gt;
-Status [Lucid Dream] chuyển thành trạng thái [Kỵ Sĩ Thời Gian], làm chậm đáng kể dòng chảy thời gian xung quanh và gây lượng lớn Spectro DMG &lt;color=Highlight&gt;upon ending the Time Rider status.&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Sức Mạnh Giấc Mơ: Trạng Thái]&lt;/color&gt;
+Trạng thái [Giấc Mơ Sáng Suốt] chuyển thành trạng thái [Kỵ Sĩ Thời Gian], làm chậm đáng kể dòng chảy thời gian xung quanh và gây lượng lớn Sát Thương Spectro &lt;color=Highlight&gt;khi kết thúc trạng thái Kỵ Sĩ Thời Gian&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
 Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ kích hoạt thêm một lần nữa khi được kích hoạt.</t>
         </is>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
 Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ kích hoạt nhiều lần khi được kích hoạt.</t>
         </is>
       </c>
@@ -7708,8 +7708,8 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Khi hiệu ứng [Sức Mạnh Giấc Mơ] gây sát thương, toàn đội nhận thêm 2,5% Tăng Sát Thương trong 0,6 giây, tối đa 100 lần cộng dồn. Hết hiệu lực thì toàn bộ cộng dồn sẽ bị xóa.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ] gây DMG, toàn đội nhận thêm 2,5% Tăng Sát Thương trong 0,6 giây, tối đa 100 lần cộng dồn. Hết hiệu lực thì toàn bộ cộng dồn sẽ bị xóa.</t>
         </is>
       </c>
     </row>
@@ -7775,8 +7775,8 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Khi hiệu ứng [Sức Mạnh Giấc Mơ] gây sát thương, toàn đội nhận Tăng Sát Thương.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ] gây DMG, toàn đội nhận Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -7842,8 +7842,8 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Giảm 50% thời gian trạng thái [Giấc Mơ Tỉnh] và tăng cường 200% hiệu quả của hiệu ứng [Sức Mạnh Giấc Mơ: Status] khi đang trong trạng thái Giấc Mơ Tỉnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Giảm 50% thời gian trạng thái [Giấc Mơ Tỉnh] và tăng cường 200% hiệu quả của hiệu ứng [Sức Mạnh Giấc Mơ: Trạng Thái] khi đang trong trạng thái Giấc Mơ Tỉnh.</t>
         </is>
       </c>
     </row>
@@ -7909,8 +7909,8 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Giảm vừa phải thời gian trạng thái [Giấc Mơ Tỉnh] và tăng cường đáng kể hiệu quả của hiệu ứng [Sức Mạnh Giấc Mơ: Status].</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Giảm vừa phải thời gian trạng thái [Giấc Mơ Tỉnh] và tăng cường đáng kể hiệu quả của hiệu ứng [Sức Mạnh Giấc Mơ: Trạng Thái].</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Giảm 20% thời gian trạng thái Giấc Mơ Tỉnh và tăng 50% HP tối đa.</t>
         </is>
       </c>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Giảm thời gian trạng thái [Giấc Mơ Tỉnh] và tăng mạnh HP tối đa.</t>
         </is>
       </c>
@@ -8110,8 +8110,8 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] không thể kích hoạt nữa, nhưng hiệu ứng [Sức Mạnh Giấc Mơ: Status] sẽ được tăng cường 200% khi ở trạng thái Giấc Mơ Tỉnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] không thể kích hoạt nữa, nhưng hiệu ứng [Sức Mạnh Giấc Mơ: Trạng Thái] sẽ được tăng cường 200% khi ở trạng thái Giấc Mơ Tỉnh.</t>
         </is>
       </c>
     </row>
@@ -8177,8 +8177,8 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] không thể kích hoạt nữa, nhưng hiệu ứng [Sức Mạnh Giấc Mơ: Status] sẽ được tăng cường mạnh mẽ.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] không thể kích hoạt nữa, nhưng hiệu ứng [Sức Mạnh Giấc Mơ: Trạng Thái] sẽ được tăng cường mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -8244,8 +8244,8 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Giảm khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] xuống 0 giây. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] chỉ có thể kích hoạt khi đang trong trạng thái Giấc Mơ Tỉnh, nhưng &lt;color=Highlight&gt;triggering them immediately ends Lucid Dream&lt;/color&gt;. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ tác động thêm 2 lần khi kích hoạt.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Giảm khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] xuống 0 giây. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] chỉ có thể kích hoạt khi đang trong trạng thái Giấc Mơ Tỉnh, nhưng &lt;color=Highlight&gt;kích hoạt chúng sẽ ngay lập tức kết thúc Giấc Mơ Tỉnh&lt;/color&gt;. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ tác động thêm 2 lần khi kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -8311,8 +8311,8 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] chỉ kích hoạt được khi ở trạng thái Giấc Mơ Tỉnh, nhưng &lt;color=Highlight&gt;triggering them immediately ends [Lucid Dream]&lt;/color&gt;. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ kích hoạt thêm 2 lần nữa.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] chỉ kích hoạt được khi ở trạng thái Giấc Mơ Tỉnh, nhưng &lt;color=Highlight&gt;kích hoạt sẽ ngay lập tức kết thúc [Giấc Mơ Tỉnh]&lt;/color&gt;. Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ kích hoạt thêm 2 lần nữa.</t>
         </is>
       </c>
     </row>
@@ -8378,8 +8378,8 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Increase Attack thêm 75%.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng ATK thêm 75%.</t>
         </is>
       </c>
     </row>
@@ -8445,8 +8445,8 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Tăng mạnh Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng mạnh ATK.</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8513,7 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. Rate]&lt;/color&gt;
-Increase Crit. Rate thêm 50%.</t>
+Tăng Crit. Rate thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Sát thương gây ra tăng thêm 75%.</t>
         </is>
       </c>
@@ -8713,8 +8713,8 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Sát thương gây ra tăng mạnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+DMG gây ra tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
 Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ tung thêm 2 đòn nữa khi ở trạng thái Giấc Mơ Tỉnh.</t>
         </is>
       </c>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
 Hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] giờ đây sẽ tung thêm đòn khi ở trạng thái [Giấc Mơ Tỉnh].</t>
         </is>
       </c>
@@ -8914,8 +8914,8 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Increase thời gian duy trì trạng thái Giấc Mơ Tỉnh lên 100% và giảm 10% Tấn Công.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Tăng thời gian duy trì trạng thái Giấc Mơ Tỉnh lên 100% và giảm 10% ATK.</t>
         </is>
       </c>
     </row>
@@ -8981,8 +8981,8 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Tăng đáng kể thời gian duy trì trạng thái Giấc Mơ Tỉnh và giảm nhẹ Tấn Công.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Tăng đáng kể thời gian duy trì trạng thái Giấc Mơ Tỉnh và giảm nhẹ ATK.</t>
         </is>
       </c>
     </row>
@@ -9048,8 +9048,8 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Giảm 25% thời gian duy trì trạng thái Giấc Mơ Tỉnh nhưng tăng 75% Tấn Công.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Giảm 25% thời gian duy trì trạng thái Giấc Mơ Tỉnh nhưng tăng 75% ATK.</t>
         </is>
       </c>
     </row>
@@ -9115,8 +9115,8 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Giảm vừa phải thời gian duy trì trạng thái Giấc Mơ Tỉnh nhưng tăng đáng kể Tấn Công.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Giảm vừa phải thời gian duy trì trạng thái Giấc Mơ Tỉnh nhưng tăng đáng kể ATK.</t>
         </is>
       </c>
     </row>
@@ -9182,8 +9182,8 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái [Lucid Dream], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ tăng thời gian duy trì thêm 1 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Sáng Suốt], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ tăng thời gian duy trì thêm 1 giây.</t>
         </is>
       </c>
     </row>
@@ -9249,8 +9249,8 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái [Lucid Dream], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ tăng thời gian duy trì.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Sáng Suốt], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ tăng thời gian duy trì.</t>
         </is>
       </c>
     </row>
@@ -9316,8 +9316,8 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;[Carnival] and [Flow]&lt;/color&gt;, gây sát thương sẽ tăng thời gian duy trì Lucid Dream thêm 1 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;[Lễ Hội] và [Dòng Chảy]&lt;/color&gt;, gây sát thương sẽ tăng thời gian duy trì Giấc Mơ Sáng Suốt thêm 1 giây.</t>
         </is>
       </c>
     </row>
@@ -9383,8 +9383,8 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;[Carnival] and [Flow]&lt;/color&gt;, gây sát thương sẽ tăng nhẹ thời gian duy trì Lucid Dream.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;[Lễ Hội] và [Dòng Chảy]&lt;/color&gt;, gây sát thương sẽ tăng nhẹ thời gian duy trì Giấc Mơ Sáng Suốt.</t>
         </is>
       </c>
     </row>
@@ -9450,8 +9450,8 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Increase khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] lên 25% và tăng Attack thêm 60%.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] lên 25% và tăng ATK thêm 60%.</t>
         </is>
       </c>
     </row>
@@ -9517,8 +9517,8 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Tăng nhẹ khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] và tăng mạnh Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng nhẹ khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] và tăng mạnh ATK.</t>
         </is>
       </c>
     </row>
@@ -9584,8 +9584,8 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;
-Giảm 15% khoảng thời gian kích hoạt của các hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] và giảm 10% Tấn Công.</t>
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
+Giảm 15% khoảng thời gian kích hoạt của các hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] và giảm 10% ATK.</t>
         </is>
       </c>
     </row>
@@ -9651,8 +9651,8 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;
-Giảm nhẹ khoảng thời gian kích hoạt của buff [Dreamscape Power: Damage] và giảm nhẹ ATK.</t>
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
+Giảm nhẹ khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] và giảm nhẹ ATK.</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
 Giảm 20% khoảng thời gian kích hoạt của các hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương].</t>
         </is>
       </c>
@@ -9785,7 +9785,8 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Giảm nhẹ khoảng thời gian kích hoạt của buff &lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
+Giảm nhẹ khoảng thời gian kích hoạt của hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương].</t>
         </is>
       </c>
     </row>
@@ -9851,8 +9852,8 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] chỉ có thể kích hoạt trong trạng thái Lucid Dream, chúng sẽ được áp dụng thêm 2 lần khi kích hoạt.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] chỉ có thể kích hoạt trong trạng thái Giấc Mơ Sáng Suốt, chúng sẽ được áp dụng thêm 2 lần khi kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -9918,8 +9919,8 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] chỉ có thể kích hoạt trong trạng thái [Lucid Dream], chúng sẽ được áp dụng nhiều lần khi kích hoạt.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] chỉ có thể kích hoạt trong trạng thái [Giấc Mơ Sáng Suốt], chúng sẽ được áp dụng nhiều lần khi kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9986,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt;
 Khi Resonator đang hoạt động gây sát thương, hồi phục 4% lượng HP đã mất của họ.</t>
         </is>
       </c>
@@ -10052,7 +10053,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt;
 Gây sát thương sẽ hồi phục một chút HP cho Resonator đang hoạt động.</t>
         </is>
       </c>
@@ -10119,8 +10120,8 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-HP tối đa hiện tại của tất cả thành viên trong đội tăng gấp đôi, nhưng giá trị sẽ bị &lt;color=Highlight&gt;fixed&lt;/color&gt; sau đó.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+HP tối đa hiện tại của tất cả thành viên trong đội tăng gấp đôi, nhưng giá trị sẽ bị &lt;color=Highlight&gt;cố định&lt;/color&gt; sau đó.</t>
         </is>
       </c>
     </row>
@@ -10186,8 +10187,8 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-HP tối đa tăng gấp đôi, nhưng giá trị sẽ bị &lt;color=Highlight&gt;fixed&lt;/color&gt; sau đó.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+HP tối đa tăng gấp đôi, nhưng giá trị sẽ bị &lt;color=Highlight&gt;cố định&lt;/color&gt; sau đó.</t>
         </is>
       </c>
     </row>
@@ -10253,8 +10254,8 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Attack hiện tại của tất cả thành viên trong đội sẽ được nhân đôi, nhưng giá trị này sẽ &lt;color=Highlight&gt;fixed&lt;/color&gt; sau đó.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+ATK hiện tại của tất cả thành viên trong đội sẽ được nhân đôi, nhưng giá trị này sẽ &lt;color=Highlight&gt;cố định&lt;/color&gt; sau đó.</t>
         </is>
       </c>
     </row>
@@ -10320,8 +10321,8 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Attack tăng gấp đôi, nhưng giá trị này sẽ &lt;color=Highlight&gt;fixed&lt;/color&gt; sau đó.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+ATK tăng gấp đôi, nhưng giá trị này sẽ &lt;color=Highlight&gt;cố định&lt;/color&gt; sau đó.</t>
         </is>
       </c>
     </row>
@@ -10387,8 +10388,8 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Yêu cầu]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; DMG (yêu cầu kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải Heavy Attack DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Đòn Nặng&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -10454,8 +10455,8 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Yêu cầu]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; DMG (yêu cầu kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải Heavy Attack DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Đòn Nặng&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10521,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Công thức Giấc Mơ: Heavy Attack</t>
+          <t>Công Thức Mộng Ảo: Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -10586,8 +10587,8 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Yêu cầu Trigger]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; DMG (yêu cầu kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -10653,8 +10654,8 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Điều Kiện Burst]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; DMG (điều kiện kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10720,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Công thức Giấc Mơ: Resonance Skill</t>
+          <t>Công Thức Mộng Ảo: Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -10785,8 +10786,8 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Điều Kiện Burst]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; DMG (điều kiện kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Đòn Cơ Bản&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -10852,8 +10853,8 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Yêu cầu]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; DMG (điều kiện kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải Basic Attack DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Đòn Cơ Bản&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10919,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Công thức Giấc Mơ: Basic Attack</t>
+          <t>Công Thức Mộng Ảo: Basic Attack</t>
         </is>
       </c>
     </row>
@@ -10984,8 +10985,8 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Yêu cầu]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; DMG (điều kiện kích hoạt cho [Ice Burst] không thay đổi), tăng vừa phải Resonance Liberation DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] không thay đổi), tăng vừa phải DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -11051,8 +11052,8 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Yêu cầu]&lt;/color&gt;
-Khi buff [Dreamscape Power: Damage] được thiết lập để kích hoạt khi gây &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; DMG (yêu cầu kích hoạt [Ice Burst] giữ nguyên), tăng vừa phải Resonance Liberation DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Điều Kiện Kích Hoạt]&lt;/color&gt;
+Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] được đặt để kích hoạt bằng cách gây &lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; (điều kiện kích hoạt của [Ice Burst] giữ nguyên), tăng vừa phải DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11118,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Công thức Giấc Mơ: Resonance Liberation</t>
+          <t>Công Thức Mộng Ảo: Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -11183,8 +11184,8 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Khi Resonator chủ động gây sát thương, tăng 15% Sát Thương và chịu thêm 5% Sát Thương trong 10 giây, tối đa 5 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Khi Resonator chủ động gây DMG, tăng 15% Sát Thương và chịu thêm 5% Sát Thương trong 10 giây, tối đa 5 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11250,8 +11251,8 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Gây sát thương sẽ làm tăng nhẹ sát thương gây ra và nhận vào của Resonator đang hoạt động.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Gây DMG sẽ làm tăng nhẹ DMG gây ra và nhận vào của Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -11317,8 +11318,8 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Khi Resonator chủ động gây sát thương, tăng 25% Sát Thương và chịu thêm 5% Sát Thương trong 10 giây, tối đa 3 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Khi Resonator chủ động gây DMG, tăng 25% Sát Thương và chịu thêm 5% Sát Thương trong 10 giây, tối đa 3 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11384,8 +11385,8 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Gây sát thương sẽ làm tăng sát thương gây ra và nhận vào của Resonator đang hoạt động.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Gây DMG sẽ làm tăng DMG gây ra và nhận vào của Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -11451,8 +11452,8 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Khi Resonator chính gây sát thương, Attack của họ tăng 15% và HP tối đa giảm 5% trong 10 giây, có thể tích lũy tối đa 5 lần. Hiệu ứng này kích hoạt mỗi 2 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Khi Resonator chính gây sát thương, ATK của họ tăng 15% và HP tối đa giảm 5% trong 10 giây, có thể tích lũy tối đa 5 lần. Hiệu ứng này kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11518,8 +11519,8 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Gây sát thương sẽ tăng nhẹ Attack của Resonator đang hoạt động và giảm nhẹ HP tối đa của họ.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Gây sát thương sẽ tăng nhẹ ATK của Resonator đang hoạt động và giảm nhẹ HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -11585,8 +11586,8 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Khi Resonator chính gây sát thương, Attack của họ tăng 25% và HP tối đa giảm 5% trong 10 giây, có thể tích lũy tối đa 3 lần. Hiệu ứng này kích hoạt mỗi 2 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Khi Resonator chính gây sát thương, ATK của họ tăng 25% và HP tối đa giảm 5% trong 10 giây, có thể tích lũy tối đa 3 lần. Hiệu ứng này kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11652,8 +11653,8 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Gây sát thương sẽ tăng Attack của Resonator đang hoạt động và giảm nhẹ HP tối đa của họ.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Gây sát thương sẽ tăng ATK của Resonator đang hoạt động và giảm nhẹ HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -11719,8 +11720,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;
-Khi Resonator đang kích hoạt đánh bại kẻ địch, giảm HP tối đa của họ đi 0.5% và tăng Crit. DMG thêm 0.02% cho &lt;color=Highlight&gt;every 1% Crit. Rate that exceeds 100% Crit. Rate&lt;/color&gt;, cộng dồn tối đa 100 lần.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; chủ động tiêu diệt kẻ địch, HP tối đa của họ sẽ giảm 0,5% và Crit. DMG tăng thêm 0,02% cho &lt;color=Highlight&gt;mỗi 1% Crit. Rate vượt quá 100% Crit. Rate&lt;/color&gt;, tối đa 100 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       <c r="M172" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;
-Tiêu diệt kẻ địch sẽ tăng nhẹ Crit. DMG của Resonator đang hoạt động dựa trên &lt;color=Highlight&gt;the excess Crit. Rate&lt;/color&gt;, đồng thời giảm nhẹ HP tối đa của họ.</t>
+Tiêu diệt kẻ địch sẽ tăng nhẹ Crit. DMG của Resonator đang hoạt động dựa trên &lt;color=Highlight&gt;phần Crit. Rate dư thừa&lt;/color&gt;, đồng thời giảm nhẹ HP tối đa của họ.</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Mỗi khi Resonator chủ động tiêu diệt kẻ địch, Tối Đa HP của họ tăng thêm 0,5%, có thể cộng dồn tối đa 100 lần.</t>
         </is>
       </c>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Tiêu diệt kẻ địch sẽ tăng nhẹ HP tối đa của Resonator đang hoạt động. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
@@ -11987,8 +11987,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;
-Khi Resonator đang kích hoạt đánh bại kẻ địch, giảm tối đa HP của họ đi 0.35% và tăng Crit. DMG thêm 0.04% cho &lt;color=Highlight&gt;every 1% Crit. Rate that exceeds 100% Crit. Rate&lt;/color&gt;, cộng dồn tối đa 50 tầng.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; chủ động tiêu diệt kẻ địch, HP tối đa của họ sẽ giảm 0,35%, và Crit. DMG tăng thêm 0,04% cho &lt;color=Highlight&gt;mỗi 1% Crit. Rate vượt quá 100% Crit. Rate&lt;/color&gt;, tối đa 50 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12054,7 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;
-Tiêu diệt kẻ địch sẽ tăng nhẹ Crit. DMG của Resonator đang hoạt động dựa trên &lt;color=Highlight&gt;the excess Crit. Rate&lt;/color&gt;, đồng thời giảm nhẹ HP tối đa.</t>
+Tiêu diệt kẻ địch sẽ tăng nhẹ Crit. DMG của Resonator đang hoạt động dựa trên &lt;color=Highlight&gt;phần Crit. Rate dư thừa&lt;/color&gt;, đồng thời giảm nhẹ HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -12121,7 +12120,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Mỗi khi Resonator chủ động tiêu diệt kẻ địch, Tối Đa HP của họ tăng thêm 1%, có thể cộng dồn tối đa 50 lần.</t>
         </is>
       </c>
@@ -12188,7 +12187,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sinh Lực]&lt;/color&gt;
 Đánh bại kẻ địch sẽ tăng Giới hạn HP tối đa của Resonator đang hoạt động.</t>
         </is>
       </c>
@@ -12255,7 +12254,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Hạ gục kẻ địch sẽ hồi 40 Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
@@ -12322,7 +12321,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Hạ gục kẻ địch sẽ hồi một lượng nhỏ Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
@@ -12389,7 +12388,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Hạ gục kẻ địch sẽ hồi 80 Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
@@ -12456,7 +12455,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Hạ gục kẻ địch sẽ hồi Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
@@ -12523,7 +12522,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Gây Bạo Kích sẽ hồi 10 Năng Lượng Giấc Mơ, gấp đôi nếu Bạo Kích được thực hiện dưới hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương].</t>
         </is>
       </c>
@@ -12590,7 +12589,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Gây Bạo Kích sẽ hồi một lượng nhỏ Năng Lượng Giấc Mơ, gấp đôi nếu Bạo Kích được thực hiện dưới hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương].</t>
         </is>
       </c>
@@ -12657,8 +12656,8 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Trạng thái Giấc Mơ Tỉnh trở nên vĩnh viễn, nhưng &lt;color=Highlight&gt;ATK will never exceed 2000&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Trạng thái Giấc Mơ Tỉnh trở nên vĩnh viễn, nhưng &lt;color=Highlight&gt;ATK của các Resonator sẽ không bao giờ vượt quá 2000&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12724,8 +12723,8 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Trạng thái Giấc Mơ Tỉnh trở nên vĩnh viễn, nhưng &lt;color=Highlight&gt;ATK will never exceed 2000&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
+Trạng thái Giấc Mơ Tỉnh trở nên vĩnh viễn, nhưng &lt;color=Highlight&gt;ATK sẽ không bao giờ vượt quá 2000&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12791,8 +12790,8 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Khi Resonator chính chịu sát thương, tăng 1 điểm Attack cho mỗi 10 HP mất, kéo dài trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Khi Resonator chính chịu DMG, tăng 1 điểm ATK cho mỗi 10 HP mất, kéo dài trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -12858,8 +12857,8 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Chịu sát thương sẽ tăng Attack dựa trên lượng HP đã mất.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Chịu DMG sẽ tăng ATK dựa trên lượng HP đã mất.</t>
         </is>
       </c>
     </row>
@@ -12925,8 +12924,8 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;
-Trong trạng thái Lucid Dream, khi các hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] gây sát thương, giảm 80% khoảng thời gian kích hoạt của tất cả hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương].</t>
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
+Trong trạng thái Giấc Mơ Sáng Suốt, khi các hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] gây sát thương, giảm 80% khoảng thời gian kích hoạt của tất cả hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương].</t>
         </is>
       </c>
     </row>
@@ -12992,8 +12991,8 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Trigger Interval]&lt;/color&gt;
-Khi ở trạng thái Lucid Dream, khi các buff [Dreamscape Power: Damage] gây DMG, giảm đáng kể trigger interval của tất cả buff [Dreamscape Power: Damage].</t>
+          <t>&lt;color=#ffd12f&gt;[Khoảng Thời Gian Kích Hoạt]&lt;/color&gt;
+Khi ở trạng thái Giấc Mơ Tỉnh Táo, khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] gây sát thương, giảm đáng kể khoảng thời gian kích hoạt của tất cả hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương].</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13058,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] gây sát thương, hồi phục 20 Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
@@ -13126,7 +13125,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi hiệu ứng [Sức Mạnh Giấc Mơ: Sát Thương] gây sát thương, hồi phục một lượng nhỏ [Năng Lượng Giấc Mơ].</t>
         </is>
       </c>
@@ -13193,8 +13192,8 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-Khi ở trạng thái Giấc Mơ Tỉnh, &lt;color=Highlight&gt;buffs that enhance the Resonator based on HP lost&lt;/color&gt; sẽ coi như Resonator chỉ còn 1 HP. HP thực tế không bị ảnh hưởng.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+Khi ở trạng thái Giấc Mơ Tỉnh, &lt;color=Highlight&gt;hiệu ứng tăng cường Resonator dựa trên lượng HP đã mất&lt;/color&gt; sẽ coi như Resonator chỉ còn 1 HP. HP thực tế không bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -13260,8 +13259,8 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-Khi ở trạng thái Giấc Mơ Tỉnh, &lt;color=Highlight&gt;buffs that enhance the Resonator based on HP lost&lt;/color&gt; sẽ coi như Resonator chỉ còn 1 HP.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+Khi ở trạng thái Giấc Mơ Tỉnh, &lt;color=Highlight&gt;hiệu ứng tăng cường Resonator dựa trên lượng HP đã mất&lt;/color&gt; sẽ coi như Resonator chỉ còn 1 HP.</t>
         </is>
       </c>
     </row>
@@ -13327,8 +13326,8 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Khi Resonator chính kích hoạt Resonance Liberation, &lt;color=Highlight&gt;consume 50% of their current HP&lt;/color&gt; để tăng Attack thêm 25% trong 10 giây. Hiệu ứng này có thể kích hoạt mỗi 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Khi Resonator chính kích hoạt Resonance Liberation, &lt;color=Highlight&gt;tiêu hao 50% HP hiện tại&lt;/color&gt; để tăng ATK thêm 25% trong 10 giây. Hiệu ứng này có thể kích hoạt mỗi 10 giây.</t>
         </is>
       </c>
     </row>
@@ -13394,8 +13393,8 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Kích hoạt Resonance Liberation sẽ &lt;color=Highlight&gt;consumes half of your current HP&lt;/color&gt; để tăng Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Kích hoạt Resonance Liberation sẽ &lt;color=Highlight&gt;tiêu hao một nửa HP hiện tại&lt;/color&gt; để tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13460,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;, &lt;color=Highlight&gt;every 1% Crit. Rate that exceeds 100% Crit. Rate&lt;/color&gt; sẽ tăng Crit. DMG thêm 2%.</t>
+          <t>Khi ở trạng thái &lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;, &lt;color=Highlight&gt;mỗi 1% Crit. Rate vượt quá 100% Crit. Rate&lt;/color&gt; sẽ tăng Crit. DMG thêm 2%.</t>
         </is>
       </c>
     </row>
@@ -13527,7 +13526,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=#ffd12f&gt;[Crit. DMG]&lt;/color&gt;, &lt;color=Highlight&gt;excess Crit. Rate&lt;/color&gt; sẽ được chuyển hóa thành Crit. DMG.</t>
+          <t>Khi ở trạng thái &lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;, &lt;color=Highlight&gt;phần Crit. Rate dư thừa&lt;/color&gt; sẽ được chuyển hóa thành Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -13593,8 +13592,8 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt;
-Khi ở trạng thái [Giấc Mơ Tỉnh], thi triển &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ tăng Tấn Công 25% và tăng 25% Sát Thương gây ra. Gây sát thương bằng Intro Skill sẽ khôi phục 20 Năng Lượng Khúc Tấu. Hiệu ứng kéo dài 6 giây, có thể chồng chất lên đến 5 lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khúc Tấu]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Tỉnh], thi triển &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ tăng ATK 25% và tăng 25% Sát Thương gây ra. Gây DMG bằng Kỹ Năng Khởi Động sẽ khôi phục 20 Năng Lượng Khúc Tấu. Hiệu ứng kéo dài 6 giây, có thể chồng chất lên đến 5 lần.</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13660,7 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt;
-Khi ở trạng thái [Giấc Mơ Tỉnh], sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ tăng vừa phải Tấn Công và Sát Thương gây ra, đồng thời hồi phục một lượng nhỏ Concerto Energy.</t>
+Khi ở trạng thái [Giấc Mơ Tỉnh], sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ tăng vừa phải ATK và Sát Thương gây ra, đồng thời hồi phục một lượng nhỏ Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -13727,8 +13726,8 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái [Lucid Dream], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ hồi phục 20 &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Sáng Suốt], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ hồi phục 20 &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13794,8 +13793,8 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái [Lucid Dream], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ hồi phục một lượng nhỏ &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Sáng Suốt], gây sát thương với hiệu ứng [Sức Mạnh Cảnh Mộng: Sát Thương] sẽ hồi phục một lượng nhỏ &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13861,8 +13860,8 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto Energy]&lt;/color&gt;
-Khi ở trạng thái [Giấc Mơ Tỉnh], gây sát thương sẽ khôi phục 10 &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Khúc Tấu]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Tỉnh], gây sát thương sẽ khôi phục 10 &lt;color=Highlight&gt;Năng Lượng Khúc Tấu&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -13928,8 +13927,8 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto Energy]&lt;/color&gt;
-Khi ở trạng thái [Giấc Mơ Tỉnh], gây sát thương sẽ hồi phục nhẹ &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Khúc Tấu]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Tỉnh], gây sát thương sẽ hồi phục nhẹ &lt;color=Highlight&gt;Năng Lượng Khúc Tấu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13995,8 +13994,8 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
-Khi ở trạng thái [Lucid Dream], sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ tăng thời gian duy trì thêm 2 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Sáng Suốt]&lt;/color&gt;
+Khi ở trạng thái [Giấc Mơ Sáng Suốt], sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ tăng thời gian duy trì thêm 2 giây.</t>
         </is>
       </c>
     </row>
@@ -14062,8 +14061,8 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
-Khi Basic Attack trúng mục tiêu, hồi 50 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 0,5 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
+Khi Đòn Cơ Bản trúng mục tiêu, hồi 50 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 0,5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14129,8 +14128,8 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
-Restore Năng Lượng Giấc Mơ khi Basic Attack trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
+Hồi phục Năng Lượng Giấc Mơ khi Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14195,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi Basic Attack trúng mục tiêu, hồi phục 20 [Năng Lượng Giấc Mơ]. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
@@ -14263,7 +14262,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi Basic Attack trúng mục tiêu, hồi phục một lượng nhỏ [Năng Lượng Giấc Mơ].</t>
         </is>
       </c>
@@ -14330,7 +14329,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi Basic Attack trúng mục tiêu, hồi phục 10 [Năng Lượng Giấc Mơ]. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
@@ -14397,7 +14396,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi Basic Attack trúng mục tiêu, hồi phục một lượng rất nhỏ [Năng Lượng Giấc Mơ].</t>
         </is>
       </c>
@@ -14464,8 +14463,8 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Increase Attack thêm 22,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng ATK thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -14531,8 +14530,8 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Tăng nhẹ Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng nhẹ ATK.</t>
         </is>
       </c>
     </row>
@@ -14598,8 +14597,8 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Increase Attack thêm 45%.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng ATK thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -14665,8 +14664,8 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Tăng Attack ở mức vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng ATK ở mức vừa phải.</t>
         </is>
       </c>
     </row>
@@ -14732,8 +14731,8 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Increase Attack thêm 67,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng ATK thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -14799,8 +14798,8 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack]&lt;/color&gt;
-Tăng mạnh Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[ATK]&lt;/color&gt;
+Tăng mạnh ATK.</t>
         </is>
       </c>
     </row>
@@ -14866,8 +14865,8 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-Increase HP tối đa thêm 22,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+Tăng HP tối đa thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -14933,7 +14932,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Tăng nhẹ HP tối đa.</t>
         </is>
       </c>
@@ -15000,8 +14999,8 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-Increase HP tối đa thêm 45%.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+Tăng HP tối đa thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15066,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Tăng HP tối đa ở mức vừa phải.</t>
         </is>
       </c>
@@ -15134,8 +15133,8 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
-Increase HP tối đa thêm 67,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
+Tăng HP tối đa thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15200,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Health]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[HP]&lt;/color&gt;
 Tăng mạnh HP tối đa.</t>
         </is>
       </c>
@@ -15268,8 +15267,8 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Increase Defense thêm 22,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng Phòng Ngự thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -15335,8 +15334,8 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Tăng Defense nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng Phòng Ngự nhẹ.</t>
         </is>
       </c>
     </row>
@@ -15402,8 +15401,8 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Increase Defense thêm 45%.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng Phòng Ngự thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -15469,8 +15468,8 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Tăng Defense ở mức vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng Phòng Ngự ở mức vừa phải.</t>
         </is>
       </c>
     </row>
@@ -15536,8 +15535,8 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Increase Defense thêm 67,5%.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng Phòng Ngự thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -15603,8 +15602,8 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Defense]&lt;/color&gt;
-Tăng mạnh chỉ số Defense.</t>
+          <t>&lt;color=#ffd12f&gt;[Phòng Ngự]&lt;/color&gt;
+Tăng mạnh chỉ số Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -15671,7 +15670,7 @@
       <c r="M230" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. Rate]&lt;/color&gt;
-Increase Crit. Rate lên 15%.</t>
+Tăng Crit. Rate lên 15%.</t>
         </is>
       </c>
     </row>
@@ -15805,7 +15804,7 @@
       <c r="M232" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. Rate]&lt;/color&gt;
-Increase Crit. Rate thêm 30%.</t>
+Tăng Crit. Rate thêm 30%.</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15938,7 @@
       <c r="M234" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;[Crit. Rate]&lt;/color&gt;
-Increase Crit. Rate thêm 45%.</t>
+Tăng Crit. Rate thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -16072,8 +16071,8 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 22,5% Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 22,5% Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16139,8 +16138,8 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng nhẹ Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng nhẹ Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16206,8 +16205,8 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 45% Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 45% Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16273,8 +16272,8 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng nhẹ Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng nhẹ Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16340,8 +16339,8 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 67,5% Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 67,5% Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -16407,8 +16406,8 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng mạnh sát thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng mạnh DMG Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -16474,8 +16473,8 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 22,5% Sát Thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 22,5% Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16541,8 +16540,8 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng nhẹ Sát Thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng nhẹ Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16608,8 +16607,8 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 45% Sát Thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 45% Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16675,8 +16674,8 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng nhẹ Sát Thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng nhẹ Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16742,8 +16741,8 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 67,5% Sát Thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 67,5% Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16809,8 +16808,8 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng mạnh sát thương Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng mạnh DMG Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -16876,8 +16875,8 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 22,5% Sát Thương Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 22,5% Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -16943,7 +16942,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Tăng nhẹ Sát Thương Resonance Skill.</t>
         </is>
       </c>
@@ -17010,8 +17009,8 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 45% Sát Thương Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 45% Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17076,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Tăng nhẹ Sát Thương Resonance Skill.</t>
         </is>
       </c>
@@ -17144,8 +17143,8 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase Sát Thương Resonance Skill thêm 67.5%.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng Sát Thương Resonance Skill thêm 67.5%.</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17210,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Tăng mạnh Sát Thương Resonance Skill.</t>
         </is>
       </c>
@@ -17278,8 +17277,8 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 22,5% Sát Thương Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 22,5% Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17344,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Tăng nhẹ Sát Thương Resonance Liberation.</t>
         </is>
       </c>
@@ -17412,8 +17411,8 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 45% Sát Thương Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 45% Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17478,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
 Tăng nhẹ Sát Thương Resonance Liberation.</t>
         </is>
       </c>
@@ -17546,8 +17545,8 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Increase 67,5% Sát Thương Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng 67,5% Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -17613,8 +17612,8 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage]&lt;/color&gt;
-Tăng mạnh sát thương Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Sát Thương]&lt;/color&gt;
+Tăng mạnh DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -17680,8 +17679,8 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Rider]&lt;/color&gt;
-Khi ở trạng thái [Kỵ Sĩ Thời Gian], gây sát thương Basic Attack sẽ trực tiếp tạo vụ nổ mà không tiêu hao [Năng Lượng Thời Gian], nhưng hệ số sát thương giảm 80%. Hiệu ứng này chỉ kích hoạt tối đa mỗi giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỵ Sĩ Thời Gian]&lt;/color&gt;
+Khi ở trạng thái [Kỵ Sĩ Thời Gian], gây DMG Basic Attack sẽ trực tiếp tạo vụ nổ mà không tiêu hao [Năng Lượng Thời Gian], nhưng hệ số DMG giảm 80%. Hiệu ứng này chỉ kích hoạt tối đa mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17747,8 +17746,8 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Rider]&lt;/color&gt;
-Khi ở trạng thái [Kỵ Sĩ Thời Gian], gây sát thương Basic Attack sẽ trực tiếp tạo vụ nổ mà không tiêu hao [Năng Lượng Thời Gian], nhưng hệ số sát thương giảm 80%. Hiệu ứng này chỉ kích hoạt tối đa mỗi giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỵ Sĩ Thời Gian]&lt;/color&gt;
+Khi ở trạng thái [Kỵ Sĩ Thời Gian], gây DMG Basic Attack sẽ trực tiếp tạo vụ nổ mà không tiêu hao [Năng Lượng Thời Gian], nhưng hệ số DMG giảm 80%. Hiệu ứng này chỉ kích hoạt tối đa mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17813,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Rider]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Kỵ Sĩ Thời Gian]&lt;/color&gt;
 Tiêu hao [Năng Lượng Thời Gian] để tạo vụ nổ sẽ tăng thời gian trạng thái Kỵ Sĩ Thời Gian thêm 1 giây.</t>
         </is>
       </c>
@@ -17881,7 +17880,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Rider]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Kỵ Sĩ Thời Gian]&lt;/color&gt;
 Tiêu hao [Năng Lượng Thời Gian] để tạo vụ nổ sẽ tăng nhẹ thời gian trạng thái Kỵ Sĩ Thời Gian.</t>
         </is>
       </c>
@@ -17948,8 +17947,8 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Energy]&lt;/color&gt;
-Đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; gây ra vụ nổ, gây 1% Fusion DMG cho mục tiêu, được tính là DMG của Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Thời Gian]&lt;/color&gt;
+Khi Basic Attack trúng mục tiêu, gây nổ và gây 1% DMG Fusion, được tính là DMG Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -18015,8 +18014,8 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Time Energy]&lt;/color&gt;
-Tấn công mục tiêu bằng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; gây một lượng rất nhỏ Fusion DMG cho mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Thời Gian]&lt;/color&gt;
+Khi Basic Attack trúng mục tiêu, gây một lượng rất nhỏ DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -18081,7 +18080,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Heavy Attack 3</t>
+          <t>Đòn Heavy Attack 3</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18275,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Heavy Attack 4</t>
+          <t>Đòn Heavy Attack 4</t>
         </is>
       </c>
     </row>
@@ -18341,7 +18340,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Mỗi khi tích lũy 30 Resonance Energy, sát thương của Đòn Tấn Công Nặng tăng thêm 18%.</t>
+          <t>Mỗi khi tích lũy 30 Resonance Energy, DMG của Đòn Heavy Attack tăng thêm 18%.</t>
         </is>
       </c>
     </row>
@@ -18406,7 +18405,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng theo Năng lượng Cộng hưởng hiện tại.</t>
+          <t>DMG Heavy Attack tăng theo Năng lượng Cộng hưởng hiện tại.</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18470,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Heavy Attack 5</t>
+          <t>Đòn Heavy Attack 5</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18535,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Đòn Tấn Công Nặng tiêu hao thêm 30 Stamina để gây thêm 35% Sát Thương.</t>
+          <t>Đòn Heavy Attack tiêu hao thêm 30 Thể Lực để gây thêm 35% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18601,7 +18600,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Tấn Công Mạnh tiêu hao Stamina để tăng Sát Thương gây ra.</t>
+          <t>Tấn Công Mạnh tiêu hao Thể Lực để tăng Sát Thương gây ra.</t>
         </is>
       </c>
     </row>
@@ -18667,8 +18666,8 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack Speed]&lt;/color&gt;
-Increase Attack Speed Basic lên 10%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tốc Độ Tấn Công]&lt;/color&gt;
+Tăng Tốc Độ Basic Attack lên 10%.</t>
         </is>
       </c>
     </row>
@@ -18734,8 +18733,8 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack Speed]&lt;/color&gt;
-Tăng rất nhẹ Attack Speed Basic.</t>
+          <t>&lt;color=#ffd12f&gt;[Tốc Độ Tấn Công]&lt;/color&gt;
+Tăng rất nhẹ Tốc Độ Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -18801,8 +18800,8 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack Speed]&lt;/color&gt;
-Increase Attack Speed Basic lên 20%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tốc Độ Tấn Công]&lt;/color&gt;
+Tăng Tốc Độ Basic Attack lên 20%.</t>
         </is>
       </c>
     </row>
@@ -18868,8 +18867,8 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Attack Speed]&lt;/color&gt;
-Tăng nhẹ Attack Speed Basic.</t>
+          <t>&lt;color=#ffd12f&gt;[Tốc Độ Tấn Công]&lt;/color&gt;
+Tăng nhẹ Tốc Độ Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18933,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên tương đương 30% HP tối đa, kéo dài 8 giây sau khi sử dụng Resonance Skill. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên tương đương 30% HP tối đa, kéo dài 8 giây sau khi sử dụng Resonance Skill. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18998,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19063,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Khi HP dưới 30%, nhận khiên tương đương 120% HP tối đa, kéo dài 10 giây. Hiệu ứng này chỉ kích hoạt mỗi 20 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Khi HP dưới 30%, nhận khiên tương đương 120% HP tối đa, kéo dài 10 giây. Hiệu ứng này chỉ kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -19129,7 +19128,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên khi HP thấp.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên khi HP thấp.</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19193,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Khi nhận khiên, Crit. DMG tăng 50% trong 12 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Khi nhận khiên, Crit. DMG tăng 50% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -19259,7 +19258,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Tăng Crit. DMG khi nhận được khiên.</t>
+          <t>Crit. DMG tăng khi nhận được khiên.</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19323,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Khi khiên tan biến, phục hồi 15% HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Khi khiên tan biến, phục hồi 15% HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19388,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; HP được phục hồi khi khiên tan biến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; HP được phục hồi khi khiên tan biến.</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19453,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Khi Dodge thành công, nhận khiên tương đương 30% HP tối đa, kéo dài 5 giây. Hiệu ứng này chỉ kích hoạt mỗi 5 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Khi né thành công, nhận khiên tương đương 30% HP tối đa, kéo dài 5 giây. Hiệu ứng này chỉ kích hoạt mỗi 5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -19519,7 +19518,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Hiệu ứng Healing tăng thêm 15% trong 20 giây sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Hiệu ứng Hồi Phục tăng thêm 15% trong 20 giây sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19583,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Hiệu ứng Healing tăng lên sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Hiệu ứng Hồi Phục tăng lên sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19648,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Phục hồi 5% HP tối đa khi đánh bại kẻ địch.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Phục hồi 5% HP tối đa khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19714,7 +19713,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; HP được phục hồi nhẹ khi đánh bại kẻ địch.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; HP được phục hồi nhẹ khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19779,7 +19778,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Phục hồi 20% HP tối đa mỗi 2 giây trong 8 giây sau khi giải phóng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Phục hồi 20% HP tối đa mỗi 2 giây trong 8 giây sau khi giải phóng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -19844,7 +19843,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; HP được phục hồi liên tục sau khi kích hoạt Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; HP được phục hồi liên tục sau khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -19909,7 +19908,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP đầy, đòn tấn công gây thêm sát thương bằng 5% HP tối đa của kẻ địch. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP đầy, đòn tấn công gây thêm sát thương bằng 5% HP tối đa của kẻ địch. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -19974,7 +19973,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP đầy, đòn tấn công gây thêm sát thương.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP đầy, đòn tấn công gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -20039,7 +20038,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Resonance Skill tiêu hao 50% HP hiện tại để tạo khiên tương đương 80% HP tối đa, kéo dài 30 giây. Hiệu ứng này chỉ kích hoạt mỗi 12 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Resonance Skill tiêu hao 50% HP hiện tại để tạo khiên tương đương 80% HP tối đa, kéo dài 30 giây. Hiệu ứng này chỉ kích hoạt mỗi 12 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -20104,7 +20103,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Tiêu hao HP khi sử dụng Resonance Skill để tạo khiên.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Tiêu hao HP khi sử dụng Resonance Skill để tạo khiên.</t>
         </is>
       </c>
     </row>
@@ -20237,10 +20236,10 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation mang lại cho bạn: 
+          <t>Kích hoạt Giải Cứu Cộng Hưởng mang lại cho bạn: 
 Mất HP mỗi giây;
 HP được phục hồi mỗi khi tấn công;
-Tấn Công và Phòng Ngự tăng mỗi khi nhận sát thương (tối đa 5 lần). Hiệu ứng kéo dài 8 giây.</t>
+ATK và Phòng Ngự tăng mỗi khi nhận DMG (tối đa 5 lần). Hiệu ứng kéo dài 8 giây.</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20304,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, bạn sẽ bị mất HP theo thời gian, đồng thời tăng Tấn Công và Phòng Ngự, và HP sẽ được hồi phục khi tấn công.</t>
+          <t>Sau khi sử dụng Resonance Liberation, bạn sẽ bị mất HP theo thời gian, đồng thời tăng ATK và Phòng Ngự, và HP sẽ được hồi phục khi tấn công.</t>
         </is>
       </c>
     </row>
@@ -20435,7 +20434,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Trong 20 giây sau khi kích hoạt Resonance Liberation, tốc độ hồi phục Stamina tăng 100%.</t>
+          <t>Trong 20 giây sau khi kích hoạt Giải Cứu Cộng Hưởng, tốc độ hồi phục Thể Lực tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -20500,7 +20499,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Resonance Liberation tăng tốc độ hồi phục Stamina.</t>
+          <t>Resonance Liberation tăng tốc độ hồi phục Thể Lực.</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20629,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Hồi phục 1 Resonance Energy khi Basic Attack trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Hồi phục 1 Resonance Energy khi Đòn Cơ Bản trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20695,7 +20694,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Energy hồi phục khi Basic Attack trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Energy hồi phục khi Đòn Cơ Bản trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20824,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Resonance Skill gây ít hơn 35% sát thương nhưng tăng 35% sát thương của Resonance Liberation trong 5 giây tiếp theo.</t>
+          <t>Resonance Skill gây ít hơn 35% DMG nhưng tăng 35% DMG của Resonance Liberation trong 5 giây tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -20890,7 +20889,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng sau khi sử dụng Resonance Skill.</t>
+          <t>DMG Resonance Liberation tăng sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -20955,7 +20954,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu Resonance Liberation giảm 50%, và Resonance Energy cần thiết cũng giảm 50%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu Resonance Liberation giảm 50%, và Resonance Energy cần thiết cũng giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21019,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Giảm Cooldown chiêu và Năng Lượng cần thiết của Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Giảm Thời gian hồi chiêu và Năng Lượng cần thiết của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -21085,7 +21084,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Vọng Âm hồi phục 15 Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Vọng Âm hồi phục 15 Năng lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -21215,7 +21214,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=#ffd12f&gt;Resonance Skill&lt;/color&gt;, &lt;color=#ffd12f&gt;Crit. Rate&lt;/color&gt; tăng 10% trong 12 giây, cộng dồn tối đa 2 lần.</t>
+          <t>Sau khi sử dụng Resonance Skill, Crit. Rate tăng thêm 10% trong 12 giây, tối đa 2 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -21280,7 +21279,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -21345,7 +21344,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Dodge tránh thành công tăng Crit. Rate lên 40% trong 3 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Né tránh thành công tăng Crit. Rate lên 40% trong 3 giây.</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21409,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng mạnh khi Dodge thành công.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng mạnh khi né thành công.</t>
         </is>
       </c>
     </row>
@@ -21475,7 +21474,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần Attack cơ bản trúng mục tiêu sẽ tăng Tốc độ Attack cơ bản thêm 4% trong 5 giây, tối đa 5 lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Mỗi lần Tấn Công cơ bản trúng mục tiêu sẽ tăng Tốc độ Tấn Công cơ bản thêm 4% trong 5 giây, tối đa 5 lần.</t>
         </is>
       </c>
     </row>
@@ -21540,7 +21539,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Tốc độ Basic Attack tăng nhẹ khi trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Tổ Hợp]&lt;/color&gt; Tốc độ Đòn Cơ Bản tăng nhẹ khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -21605,7 +21604,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu Resonance Skill giảm 20%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu Resonance Skill giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -21670,7 +21669,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu Resonance Skill được rút ngắn.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu Resonance Skill được rút ngắn.</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21734,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Dodge tránh thành công sẽ hồi phục 10 Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Né tránh thành công sẽ hồi phục 10 Năng lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -21800,7 +21799,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Concerto Energy được hồi phục khi Dodge thành công.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Concerto Energy được hồi phục khi né thành công.</t>
         </is>
       </c>
     </row>
@@ -21865,7 +21864,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Vọng Âm hồi phục 10 Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Vọng Âm hồi phục 10 Năng lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21929,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Concerto Energy của Kỹ Năng Vọng Âm đã hồi phục nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Năng lượng Concerto của Kỹ Năng Vọng Âm đã hồi phục nhẹ.</t>
         </is>
       </c>
     </row>
@@ -21995,7 +21994,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Intro Skill tăng sát thương Kỹ Năng Echo lên 40% trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Kỹ Năng Khởi Động tăng DMG Kỹ Năng Echo lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22059,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sử dụng Intro Skill làm tăng Sát Thương Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Sử dụng Kỹ Năng Khởi Động làm tăng Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22124,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Intro Skill tăng 12% Tấn Công trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Khởi Động tăng 12% ATK trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -22190,7 +22189,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng nhẹ sau khi sử dụng Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng nhẹ sau khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22254,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; HP tối đa tăng 1% cho mỗi khiên nhận được, tối đa 30 lần chồng chất.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; HP tối đa tăng 1% cho mỗi khiên nhận được, tối đa 30 lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -22320,7 +22319,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; HP tối đa tăng nhẹ cho mỗi khiên nhận được.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; HP tối đa tăng nhẹ cho mỗi khiên nhận được.</t>
         </is>
       </c>
     </row>
@@ -22450,7 +22449,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng mạnh sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng mạnh sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -22580,7 +22579,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng mạnh sau khi sử dụng Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng mạnh sau khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22774,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sử dụng Resonance Liberation sẽ đặt lại Cooldown chiêu và khôi phục 100% Resonance Energy. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sử dụng Resonance Liberation sẽ đặt lại Thời gian hồi chiêu và khôi phục 100% Resonance Energy. Hiệu ứng này chỉ kích hoạt mỗi 15 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -22905,7 +22904,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Basic Attack trúng mục tiêu sẽ giảm 1% Cooldown chiêu của Resonance Skill và Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Đòn Basic Attack trúng mục tiêu sẽ giảm 1% Thời gian hồi chiêu của Resonance Skill và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -22970,7 +22969,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu của Resonance Skill và Resonance Liberation giảm nhẹ sau mỗi đòn Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm nhẹ sau mỗi đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -23035,7 +23034,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Khi bị tấn công, nhận khiên tương đương 15% HP tối đa trong 8 giây. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Khi bị tấn công, nhận khiên tương đương 15% HP tối đa trong 8 giây. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23100,7 +23099,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Resonance Liberation sẽ hồi phục 100% Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Resonance Liberation sẽ hồi phục 100% Năng lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23229,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Intro Skill hồi phục 100% Concerto Energy. Có thể kích hoạt mỗi 20 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Kỹ Năng Khởi Động hồi phục 100% Năng lượng Concerto. Có thể kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23295,7 +23294,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Nhận được lượng lớn Concerto Energy sau khi sử dụng Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Nhận được lượng lớn Concerto Energy sau khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -23360,7 +23359,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Intro Skill giảm 30% Cooldown chiêu Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Kỹ Năng Khởi Động giảm 30% Thời gian hồi chiêu Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -23425,7 +23424,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo giảm khi sử dụng Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo giảm khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -23555,7 +23554,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Intro Skill giảm 50% Cooldown chiêu của Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Kỹ Năng Khởi Động giảm 50% Thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23619,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu Resonance Skill giảm đáng kể sau khi sử dụng Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu Resonance Skill giảm đáng kể sau khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -23685,7 +23684,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Intro Skill hồi phục 30 Resonance Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Kỹ Năng Khởi Động hồi phục 30 Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -23750,7 +23749,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Energy hồi phục từ Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Energy hồi phục từ Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -23815,7 +23814,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP ở mức 100%, mọi Basic Attack sẽ kích hoạt "Effect Vỡ", gây sát thương bằng 40% Tấn Công lên mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP ở mức 100%, mọi Đòn Basic Attack sẽ kích hoạt "Hiệu Ứng Vỡ", gây sát thương bằng 40% ATK lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23879,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP đầy, mọi đòn tấn công sẽ kích hoạt "Effect Vỡ".</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP đầy, mọi đòn tấn công sẽ kích hoạt "Hiệu Ứng Vỡ".</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23944,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Khi tấn công trúng mục tiêu 20 lần, "Meteor Fire" sẽ được triệu hồi để tấn công, gây sát thương bằng 800% Tấn Công lên các mục tiêu trong phạm vi.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Khi tấn công trúng mục tiêu 20 lần, "Meteor Fire" sẽ được triệu hồi để tấn công, gây DMG bằng 800% ATK lên các mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -24010,7 +24009,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Triệu hồi "Hỏa Meteorit" tấn công khu vực khi tấn công trúng mục tiêu đủ số lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Tổ Hợp]&lt;/color&gt; Triệu hồi "Hỏa Meteorit" tấn công khu vực khi tấn công trúng mục tiêu đủ số lần.</t>
         </is>
       </c>
     </row>
@@ -24075,7 +24074,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Đòn chí mạng kích hoạt "Effect Hợp Nhất", gây sát thương bằng 150% Tấn Công lên kẻ địch.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Đòn chí mạng kích hoạt "Hiệu Ứng Hợp Nhất", gây DMG bằng 150% ATK lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24139,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Kích hoạt "Effect Hòa Nhập" khi xuất hiện bạo kích.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Kích hoạt "Hiệu Ứng Hòa Nhập" khi xuất hiện bạo kích.</t>
         </is>
       </c>
     </row>
@@ -24205,7 +24204,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Khi tấn công trúng mục tiêu 20 lần, sát thương của Resonance Skill và Resonance Liberation tăng 80% trong 6 giây. Hiệu ứng này chỉ kích hoạt mỗi 20 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Combo]&lt;/color&gt; Khi tấn công trúng mục tiêu 20 lần, DMG của Resonance Skill và Resonance Liberation tăng 80% trong 6 giây. Hiệu ứng này chỉ kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24335,7 +24334,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Khi có khiên, Resonance Skill hoặc Resonance Liberation sẽ kích hoạt "Effect Vỡ Shield", gây sát thương bằng 350% Tấn Công lên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 3 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Khi có khiên, Resonance Skill hoặc Resonance Liberation sẽ kích hoạt "Hiệu Ứng Vỡ Khiên", gây DMG bằng 350% ATK lên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24400,7 +24399,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Resonance Skill hoặc Resonance Liberation kích hoạt "Effect Vỡ Shield" khi đang có khiên.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Resonance Skill hoặc Resonance Liberation kích hoạt "Hiệu Ứng Vỡ Khiên" khi đang có khiên.</t>
         </is>
       </c>
     </row>
@@ -24465,7 +24464,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Khi có khiên, mỗi lần nhận sát thương sẽ kích hoạt "Effect Chuông Băng", gây sát thương bằng 500% Tấn Công lên mục tiêu trong phạm vi nhất định. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Khi có khiên, mỗi lần nhận DMG sẽ kích hoạt "Hiệu Ứng Chuông Băng", gây DMG bằng 500% ATK lên mục tiêu trong phạm vi nhất định. Hiệu ứng này chỉ kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24530,7 +24529,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Intro Skill tăng 50% Tấn Công trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Kỹ Năng Khởi Động tăng 50% ATK trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -24595,7 +24594,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát thương gây ra tăng đáng kể sau khi sử dụng Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sát thương gây ra tăng đáng kể sau khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -24660,7 +24659,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Resonance Skill tăng 50% Tấn Công trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Resonance Skill tăng 50% ATK trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -24725,7 +24724,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng mạnh sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng mạnh sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24789,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sát thương Kỹ Năng Echo tăng 75%.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; DMG Kỹ Năng Echo tăng 75%.</t>
         </is>
       </c>
     </row>
@@ -24855,7 +24854,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sát thương Kỹ Năng Echo tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; DMG Kỹ Năng Echo tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -24920,7 +24919,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Kỹ Năng Vọng Âm tăng Crit. DMG lên 80% trong 15 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Kỹ Năng Vọng Âm tăng Crit. DMG lên 80% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -24985,7 +24984,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng đáng kể sau khi sử dụng Kỹ Năng Echo.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. DMG tăng đáng kể sau khi sử dụng Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25049,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Resonance Liberation tăng 50% Tấn Công trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Resonance Liberation tăng 50% ATK trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25114,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng mạnh sau khi kích hoạt Resonance Liberation.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng mạnh sau khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -25180,7 +25179,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sau khi sử dụng Resonance Skill, sát thương gây ra tăng 20%, Speed Đánh Basic và Movement Speed tăng 20% trong 8 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sau khi sử dụng Resonance Skill, sát thương gây ra tăng 20%, Tốc Độ Đánh Cơ Bản và Tốc Độ Di Chuyển tăng 20% trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -25245,7 +25244,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Increase Sát thương gây ra, Attack Speed Basic và Movement Speed sau khi sử dụng Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Tăng Sát thương gây ra, Tốc Độ Basic Attack và Tốc Độ Di Chuyển sau khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25309,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng 75%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng 75%.</t>
         </is>
       </c>
     </row>
@@ -25375,7 +25374,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -25440,7 +25439,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP ở mức 100%, Tấn Công, sát thương gây ra và Crit. Rate tăng 22%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP ở mức 100%, ATK, sát thương gây ra và Crit. Rate tăng 22%.</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25504,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Khi HP đầy, Tấn Công, sát thương gây ra và Crit. Rate đều tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Khi HP đầy, ATK, sát thương gây ra và Crit. Rate đều tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25569,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Sau khi bị tấn công, hồi phục 1% HP tối đa mỗi 2 giây trong 10 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt; Sau khi bị tấn công, hồi phục 1% HP tối đa mỗi 2 giây trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25634,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Liên tục hồi phục HP sau khi bị tấn công.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt; Liên tục hồi phục HP sau khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25699,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Mỗi đòn Basic Attack trúng mục tiêu sẽ hồi phục 1 Concerto Energy. Có thể kích hoạt mỗi giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Mỗi đòn Basic Attack trúng mục tiêu sẽ hồi phục 1 Năng lượng Concerto. Có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -25765,7 +25764,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Concerto Energy được hồi phục nhẹ khi Basic Attack trúng mục tiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Concerto Energy được hồi phục nhẹ khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -25895,7 +25894,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng theo lượng Resonance Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng theo lượng Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25959,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng 16%.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng 16%.</t>
         </is>
       </c>
     </row>
@@ -26025,7 +26024,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. Rate tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. Rate tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26154,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương gây ra tăng theo lượng STA.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG gây ra tăng theo lượng STA.</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26219,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo giảm 50%.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -26285,7 +26284,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo giảm.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo giảm.</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26349,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng 60%.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. DMG tăng 60%.</t>
         </is>
       </c>
     </row>
@@ -26415,7 +26414,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Tăng mạnh Crit. DMG.</t>
+          <t>Crit. DMG tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26479,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 12%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 12%.</t>
         </is>
       </c>
     </row>
@@ -26545,7 +26544,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26609,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 24%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 24%.</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26674,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26739,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 48%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 48%.</t>
         </is>
       </c>
     </row>
@@ -26805,7 +26804,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng mạnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -26870,7 +26869,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát thương Đòn Đánh Basic tăng 18%.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; DMG Đòn Đánh Cơ Bản tăng 18%.</t>
         </is>
       </c>
     </row>
@@ -26935,7 +26934,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát Thương Basic Attack tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sát Thương Basic Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -27000,7 +26999,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Increase 36% Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Tăng 36% Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27064,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát Thương Basic Attack tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sát Thương Basic Attack tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27129,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Increase 72% Sát Thương Basic Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Tăng 72% Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27194,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Sát Thương Basic Attack tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; Sát Thương Basic Attack tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27259,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng 18%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng 18%.</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27324,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27389,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng 36%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng 36%.</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27454,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27519,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng 72%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng 72%.</t>
         </is>
       </c>
     </row>
@@ -27585,7 +27584,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Skill tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Skill tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -27650,7 +27649,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng 15%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng 15%.</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27714,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng nhẹ.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27779,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng 30%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng 30%.</t>
         </is>
       </c>
     </row>
@@ -27845,7 +27844,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng vừa phải.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -27910,7 +27909,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng 60%.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng 60%.</t>
         </is>
       </c>
     </row>
@@ -27975,7 +27974,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Sát thương Resonance Liberation tăng đáng kể.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; DMG Resonance Liberation tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -28040,7 +28039,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Giới hạn STA tối đa tăng thêm 100%.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Giới hạn STA tối đa tăng thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -28105,7 +28104,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Tăng đáng kể giới hạn STA tối đa.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi Phục]&lt;/color&gt; Tăng đáng kể giới hạn STA tối đa.</t>
         </is>
       </c>
     </row>
@@ -28170,7 +28169,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 50% trong 8 giây sau khi sử dụng Grapple.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 50% trong 8 giây sau khi sử dụng Móc Câu.</t>
         </is>
       </c>
     </row>
@@ -28235,7 +28234,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng sau khi sử dụng Grapple.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng sau khi sử dụng Grapple.</t>
         </is>
       </c>
     </row>
@@ -28300,7 +28299,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Cooldown chiêu của Móc câu giảm 5 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt; Thời gian hồi chiêu của Móc câu giảm 5 giây.</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28364,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Healing]&lt;/color&gt; Cooldown chiêu của Móc câu được rút ngắn.</t>
+          <t>&lt;color=#ffd12f&gt;[Hồi phục]&lt;/color&gt; Thời gian hồi chiêu của Móc câu được rút ngắn.</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28819,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Khi nhận khiên, Cooldown chiêu Kỹ Năng Echo giảm 20%.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Khi nhận khiên, Thời gian hồi chiêu Kỹ Năng Echo giảm 20%.</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28884,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Cooldown chiêu Kỹ Năng Echo giảm khi nhận được khiên.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Thời gian hồi chiêu Kỹ Năng Echo giảm khi nhận được khiên.</t>
         </is>
       </c>
     </row>
@@ -29210,7 +29209,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Một Lốc Xoáy được tạo ra sau khi đánh bại kẻ địch (Hồi chiêu 5 giây)</t>
+          <t>Một Lốc Xoáy được tạo ra sau khi đánh bại kẻ địch (Thời gian hồi 5 giây)</t>
         </is>
       </c>
     </row>
@@ -29275,7 +29274,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Cyclone xuất hiện sau khi đánh bại kẻ địch</t>
+          <t>Xoáy Lốc xuất hiện sau khi đánh bại kẻ địch</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29599,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tấn Công tăng 18% sau khi sử dụng móc câu trong 12 giây.</t>
+          <t>ATK tăng 18% sau khi sử dụng móc câu trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29729,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Khi xuất hiện bạo kích, nhận 2 Resonance Energy. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Khi xuất hiện bạo kích, nhận 2 Resonance Energy. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -29795,7 +29794,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Nhận thêm Resonance Energy khi xuất hiện bạo kích.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Nhận thêm Resonance Energy khi xuất hiện bạo kích.</t>
         </is>
       </c>
     </row>
@@ -29990,7 +29989,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng 64%, nhưng Energy Regen giảm 50%.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. DMG tăng 64%, nhưng Hồi Năng Lượng giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30054,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Crit. DMG tăng mạnh, nhưng Energy Regen giảm.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Crit. DMG tăng mạnh, nhưng Hồi Năng Lượng giảm.</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30119,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Khi xuất hiện bạo kích, Tấn Công tăng 10% trong 7 giây, tối đa chồng 10 lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Khi xuất hiện bạo kích, ATK tăng 10% trong 7 giây, tối đa chồng 10 lần.</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30184,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; ATK sau khi ra đòn chí mạng, có thể cộng dồn.</t>
+          <t>ATK tăng sau mỗi đòn bạo kích, có thể cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -30250,7 +30249,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Khi đạt Critical Hit, Tấn Công tăng 10% trong 15 giây, tối đa 2 lần cộng dồn.</t>
+          <t>Khi đạt Bạo Kích, ATK tăng 10% trong 15 giây, tối đa 2 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -30315,7 +30314,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Critical Hit tăng Tấn Công.</t>
+          <t>Bạo Kích tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -30381,8 +30380,8 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Critical Hit]&lt;/color&gt;
-Khi ra đòn bạo kích, Attack Speed cơ bản tăng 5% trong 15 giây, tối đa 4 lần cộng dồn. Hiệu ứng này chỉ kích hoạt mỗi 2 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Cú Đánh Bạo Kích]&lt;/color&gt;
+Khi ra đòn bạo kích, Tốc Độ Tấn Công cơ bản tăng 5% trong 15 giây, tối đa 4 lần cộng dồn. Hiệu ứng này chỉ kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -30447,7 +30446,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Tốc độ &lt;color=#ffd12f&gt;[Basic Attack]&lt;/color&gt; tăng nhẹ khi ra đòn &lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt;.</t>
+          <t>Tốc độ Basic Attack tăng nhẹ sau mỗi đòn bạo kích.</t>
         </is>
       </c>
     </row>
@@ -30512,7 +30511,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Mỗi lần &lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; sẽ phục hồi 8 Resonance Energy. Hiệu ứng này có thể kích hoạt mỗi 2 giây 1 lần.</t>
+          <t>Mỗi lần ra đòn bạo kích sẽ hồi 8 Resonance Energy. Hiệu ứng này chỉ kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30576,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Crit. Hit]&lt;/color&gt; Resonance Energy hồi phục nhẹ khi xuất hiện bạo kích.</t>
+          <t>&lt;color=#ffd12f&gt;[Bạo Kích]&lt;/color&gt; Resonance Energy hồi phục nhẹ khi xuất hiện bạo kích.</t>
         </is>
       </c>
     </row>
@@ -30642,7 +30641,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Tiêu diệt mục tiêu sẽ hồi phục 20 Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Tiêu diệt mục tiêu sẽ hồi phục 20 Năng lượng Concerto.</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30771,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Cooldown Móc giảm đáng kể.</t>
+          <t>Thời gian hồi Móc giảm đáng kể.</t>
         </is>
       </c>
     </row>
@@ -30837,7 +30836,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Cooldown Móc giảm đáng kể.</t>
+          <t>Thời gian hồi Móc giảm đáng kể.</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30901,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Grapple, Sát Thương gây ra tăng 18% trong 12 giây.</t>
+          <t>Sau khi sử dụng Móc Câu, Sát Thương gây ra tăng 18% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -30967,7 +30966,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Sát thương tăng lên sau khi sử dụng Grapple</t>
+          <t>DMG tăng lên sau khi sử dụng Grapple</t>
         </is>
       </c>
     </row>
@@ -31032,7 +31031,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Giảm Phòng Ngự cơ bản &lt;color=#ff5454&gt;60%&lt;/color&gt; và nhận thêm &lt;color=#3cea36&gt;50%&lt;/color&gt; Dream Fragments.</t>
+          <t>Giảm Phòng Ngự cơ bản &lt;color=#ff5454&gt;60%&lt;/color&gt; và nhận thêm &lt;color=#3cea36&gt;50%&lt;/color&gt; Mảnh Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -31103,13 +31102,13 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo để triệu hồi Thundering Mephis, thực hiện tối đa 6 đòn tấn công chớp nhoáng. Nếu không kích hoạt lại Kỹ Năng Echo trong một khoảng thời gian nhất định, nó sẽ bước vào Cooldown chiêu.
+          <t>Kích hoạt Kỹ Năng Echo để triệu hồi Thundering Mephis, thực hiện tối đa 6 đòn tấn công chớp nhoáng. Nếu không kích hoạt lại Kỹ Năng Echo trong một khoảng thời gian nhất định, nó sẽ bước vào thời gian hồi chiêu.
 - Điện Áp Ẩn
-Khi Resonator thực hiện Heavy Attack hoặc Resonance Skill, họ sẽ nhận Điện Áp Ẩn, tối đa 3 tầng.
-Mỗi đòn tấn công chớp nhoáng của Thundering Mephis sẽ tiêu hao 1 tầng Điện Áp Ẩn, gây thêm Electro DMG bằng 250% Attack.
+Khi Resonator thực hiện Đòn Heavy Attack hoặc Resonance Skill, họ sẽ nhận Điện Áp Ẩn, tối đa 3 tầng.
+Mỗi đòn tấn công chớp nhoáng của Thundering Mephis sẽ tiêu hao 1 tầng Điện Áp Ẩn, gây thêm Sát Thương Electro bằng 250% ATK.
 - Điện Giật
 Mỗi đòn tấn công chớp nhoáng của Thundering Mephis sẽ cấp Điện Giật, tối đa 3 tầng.
-Khi tấn công kẻ địch bằng Basic Attack, 1 tầng Điện Giật sẽ bị tiêu hao, giải phóng một đòn sét mạnh gây Electro DMG bằng 250% Attack của Resonator lên kẻ địch.</t>
+Khi tấn công kẻ địch bằng Đòn Basic Attack, 1 tầng Điện Giật sẽ bị tiêu hao, giải phóng một đòn sét mạnh gây Sát Thương Electro bằng 250% ATK của Resonator lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -31174,7 +31173,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Nhận Điện Áp Ẩn sau khi sử dụng Resonance Skill và Heavy Attack. Nhận Đòn Điện Sau khi tung ra các đòn tấn công chớp nhoáng của Thundering Mephis.</t>
+          <t>Nhận Điện Áp Ẩn sau khi sử dụng Resonance Skill và Đòn Heavy Attack. Nhận Đòn Điện Sau khi tung ra các đòn tấn công chớp nhoáng của Thundering Mephis.</t>
         </is>
       </c>
     </row>
@@ -31304,7 +31303,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Giới hạn của Điện Áp Ẩn tăng lên 6 lớp. Mỗi lớp Điện Áp Ẩn tiêu hao sẽ gây Electro DMG tương đương 250% Tấn Công của Resonator.</t>
+          <t>Giới hạn của Điện Áp Ẩn tăng lên 6 lớp. Mỗi lớp Điện Áp Ẩn tiêu hao sẽ gây Sát Thương Electro tương đương 250% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -31369,7 +31368,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Increase giới hạn tích lũy của Cloaked Voltage và sát thương của nó.</t>
+          <t>Tăng giới hạn tích lũy của Cloaked Voltage và DMG của nó.</t>
         </is>
       </c>
     </row>
@@ -31434,7 +31433,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Sau 6 đòn tấn công chớp nhoáng, Mephis Sấm Sét sẽ tung ra một đòn kết liễu mạnh mẽ, hút kẻ địch xung quanh và gây Sát Thương Điện bằng 320%+800% Attack của Resonator. Mỗi tầng Điện Áp Ẩn sẽ tăng Sát Thương đòn kết liễu thêm 100%. Sau khi tung đòn kết liễu, Resonator sẽ nhận một lá chắn tương đương 10% HP tối đa trong 2 giây.</t>
+          <t>Sau 6 đòn tấn công chớp nhoáng, Mephis Sấm Sét sẽ tung ra một đòn kết liễu mạnh mẽ, hút kẻ địch xung quanh và gây Sát Thương Điện bằng 320%+800% ATK của Resonator. Mỗi tầng Điện Áp Ẩn sẽ tăng Sát Thương đòn kết liễu thêm 100%. Sau khi tung đòn kết liễu, Resonator sẽ nhận một lá chắn tương đương 10% HP tối đa trong 2 giây.</t>
         </is>
       </c>
     </row>
@@ -31499,7 +31498,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, tự động tiêu hao toàn bộ để triệu hồi Đồng Hành Concerto. Đồng Hành Concerto sẽ tự động thi triển Kỹ Năng Khởi Đầu và Kỹ Năng Kết Thúc trước khi rời chiến trường. Sát thương Kỹ Năng Khởi Đầu của Đồng Hành Concerto tăng thêm {0}.</t>
+          <t>Khi Năng lượng Concerto đầy, tự động tiêu hao toàn bộ để triệu hồi Đồng Hành Concerto. Đồng Hành Concerto sẽ tự động thi triển Kỹ Năng Khởi Đầu và Outro Skill trước khi rời chiến trường. DMG Kỹ Năng Khởi Đầu của Đồng Hành Concerto tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -31564,7 +31563,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, tự động tiêu hao toàn bộ để triệu hồi Đồng Hành Concerto. Đồng Hành Concerto gây thêm sát thương.</t>
+          <t>Khi Năng lượng Concerto đầy, tự động tiêu hao toàn bộ để triệu hồi Đồng Hành Concerto. Đồng Hành Concerto gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -31629,7 +31628,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi kích hoạt Resonance Liberation, bước vào trạng thái "Unlimited Firepower" trong {1} giây, "Đạn Nhiệt Áp" ngay lập tức được nạp đầy và không bị tiêu hao; sát thương "DAKA DAKA!" tăng thêm {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi kích hoạt Resonance Liberation, bước vào trạng thái "Hỏa Lực Vô Hạn" trong {1} giây, "Đạn Nhiệt Áp" ngay lập tức được nạp đầy và không bị tiêu hao; DMG "DAKA DAKA!" tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -31698,7 +31697,7 @@
       <c r="M475" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; "DAKA DAKA!" nhận các nâng cấp đặc biệt sau:
-- Cooldown chiêu Resonance Skill được đặt lại một lần khi vào trạng thái "DAKA DAKA!"
+- Thời gian hồi chiêu Resonance Skill được đặt lại một lần khi vào trạng thái "DAKA DAKA!"
 - Có thể sử dụng Resonance Skill để thi triển "Tinh Thần Chiến Đấu Vút Bay" trong trạng thái "DAKA DAKA!". Nếu "Đạn Nhiệt Áp" chưa cạn, sẽ vào lại trạng thái "DAKA DAKA!"
 - Sát Thương của "Tinh Thần Chiến Đấu Vút Bay" tăng thêm {0}.</t>
         </is>
@@ -31895,7 +31894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack kích hoạt thêm Vụ Nổ Điện Từ khi đánh dấu Sinner's Mark lên kẻ địch. Trigger Vụ Nổ Điện Từ, Thunder Cuồng Nộ hoặc Đòn Phán Xét sẽ tăng Electro DMG thêm {0}, tối đa cộng dồn {1} lần trong {2} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack kích hoạt thêm Vụ Nổ Điện Từ khi đánh dấu Dấu Ấn Tội Nhân lên kẻ địch. Kích hoạt Vụ Nổ Điện Từ, Sấm Sét Cuồng Nộ hoặc Đòn Phán Xét sẽ tăng DMG Electro thêm {0}, tối đa cộng dồn {1} lần trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -32025,7 +32024,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Trong trạng thái "DAKA DAKA!", mỗi {0} giây sẽ nhận được {1} tầng "DAKA DAKA!" tăng cường, tăng Fusion DMG {2}, tối đa {3} tầng. Hiệu ứng kéo dài đến {4} giây sau khi "DAKA DAKA!" kết thúc.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Trong trạng thái "DAKA DAKA!", mỗi {0} giây sẽ nhận được {1} tầng "DAKA DAKA!" tăng cường, tăng Sát Thương Fusion {2}, tối đa {3} tầng. Hiệu ứng kéo dài đến {4} giây sau khi "DAKA DAKA!" kết thúc.</t>
         </is>
       </c>
     </row>
@@ -32155,7 +32154,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Kích hoạt "Tinh thần chiến đấu vùn vụt" để ngắt "DAKA DAKA!". Ngoài ra, cứ mỗi 0,5 giây trong trạng thái "DAKA DAKA!" sẽ giảm 1 giây Cooldown chiêu của Skill Cộng hưởng.</t>
+          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Kích hoạt "Tinh thần chiến đấu vùn vụt" để ngắt "DAKA DAKA!". Ngoài ra, cứ mỗi 0,5 giây trong trạng thái "DAKA DAKA!" sẽ giảm 1 giây Thời gian hồi chiêu của Kỹ năng Cộng hưởng.</t>
         </is>
       </c>
     </row>
@@ -32220,7 +32219,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Kích hoạt "Tinh thần chiến đấu vùn vụt" để ngắt "DAKA DAKA!". Ngoài ra, cứ mỗi 0,5 giây trong trạng thái "DAKA DAKA!" sẽ giảm 1 giây Cooldown chiêu của Skill Cộng hưởng.</t>
+          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Kích hoạt "Tinh thần chiến đấu vùn vụt" để ngắt "DAKA DAKA!". Ngoài ra, cứ mỗi 0,5 giây trong trạng thái "DAKA DAKA!" sẽ giảm 1 giây Thời gian hồi chiêu của Kỹ năng Cộng hưởng.</t>
         </is>
       </c>
     </row>
@@ -32415,7 +32414,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; "DAKA DAKA!" giảm Fusion RES DMG của mục tiêu {0} khi trúng đích trong {1} giây, tối đa {2} lần chồng chất.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; "DAKA DAKA!" giảm Kháng Sát Thương Fusion của mục tiêu {0} khi trúng đích trong {1} giây, tối đa {2} lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -32480,7 +32479,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; "DAKA DAKA!" ngoài ra còn làm giảm Fusion RES DMG của kẻ địch.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; "DAKA DAKA!" ngoài ra còn làm giảm Kháng Sát Thương Fusion của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -32549,7 +32548,7 @@
       <c r="M488" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Boom Boom nhận các hiệu ứng đặc biệt sau:
-- Khi kích hoạt "Boom Boom", sẽ có thêm {0} viên "Thermobaric Bullets".
+- Khi kích hoạt "Boom Boom", sẽ có thêm {0} viên "Đạn Nhiệt Áp".
 - Dodge Counter có thể kích hoạt "Boom Boom".
 - Sát Thương "Boom Boom" tăng thêm {1}.</t>
         </is>
@@ -32681,7 +32680,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Basic Attack]&lt;/color&gt; Sát thương do Taoqi gây ra tăng thêm 90%. Khi Basic Attack trúng mục tiêu, có 50% cơ hội hồi 1 Điểm Quyết Tâm.</t>
+          <t>&lt;color=#ffd12f&gt;[Đòn Cơ Bản]&lt;/color&gt; Sát thương do Taoqi gây ra tăng thêm 90%. Khi Đòn Cơ Bản trúng mục tiêu, có 50% cơ hội hồi 1 Điểm Quyết Tâm.</t>
         </is>
       </c>
     </row>
@@ -32746,7 +32745,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Basic Attack]&lt;/color&gt; Basic Attack có thể hồi Phục Định Lượng.</t>
+          <t>&lt;color=#ffd12f&gt;[Đòn Cơ Bản]&lt;/color&gt; Đòn Cơ Bản có thể hồi Phục Định Lượng.</t>
         </is>
       </c>
     </row>
@@ -32876,7 +32875,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Chiến Thuật Dodge Đòn bổ sung hiệu ứng kéo diện rộng và tăng đáng kể Phòng Ngự.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Chiến Thuật Né Đòn bổ sung hiệu ứng kéo diện rộng và tăng đáng kể Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -32941,7 +32940,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Tất cả sát thương gây ra bởi Taoqi tăng 90%, và đòn cuối của "Phản Đòn Định Thời" sẽ gây thêm 330% Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Tất cả DMG gây ra bởi Taoqi tăng 90%, và đòn cuối của "Phản Đòn Định Thời" sẽ gây thêm 330% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33005,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Tất cả sát thương gây ra được tăng đáng kể, đồng thời sát thương của đòn cuối trong "Phản Đòn Định Thời" cũng tăng mạnh.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Tất cả DMG gây ra được tăng đáng kể, đồng thời DMG của đòn cuối trong "Phản Đòn Định Thời" cũng tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33070,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Tất cả sát thương gây ra được tăng thêm {0}. Khi "Phòng Thủ Vững Chắc" duy trì trên {1} giây, phản đòn sẽ tự động kích hoạt, và sát thương Basic Attack tăng thêm {2} trong {3} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Tất cả DMG gây ra được tăng thêm {0}. Khi "Phòng Thủ Vững Chắc" duy trì trên {1} giây, phản đòn sẽ tự động kích hoạt, và DMG Basic Attack tăng thêm {2} trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -33136,7 +33135,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Tất cả sát thương được tăng đáng kể. Phản đòn sẽ kích hoạt sớm hơn khi tích năng đòn Heavy Attack. Sát thương Basic Attack tăng mạnh trong thời gian ngắn.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Tất cả DMG được tăng đáng kể. Phản đòn sẽ kích hoạt sớm hơn khi tích năng đòn Heavy Attack. DMG Basic Attack tăng mạnh trong thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -33201,7 +33200,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Mỗi lần Phản Đòn Định Thời tiêu hao Năng Lượng Forte, Cooldown chiêu của Resonance Skill giảm {0} giây. Đồng thời tăng {1} Havoc DMG, tối đa {2} tầng trong {3} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Mỗi lần Phản Đòn Định Thời tiêu hao Năng Lượng Forte, Thời gian hồi chiêu của Resonance Skill giảm {0} giây. Đồng thời tăng {1} Sát Thương Havoc, tối đa {2} tầng trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -33266,7 +33265,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Cooldown chiêu của Resonance Skill giảm khi Phản Đòn tiêu hao Năng Lượng Forte. Ngoài ra, Havoc DMG cũng tăng nhẹ.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Thời gian hồi chiêu của Resonance Skill giảm khi Phản Đòn tiêu hao Năng Lượng Forte. Ngoài ra, Sát Thương Havoc cũng tăng nhẹ.</t>
         </is>
       </c>
     </row>
